--- a/reports/jobs_2026-09-20.xlsx
+++ b/reports/jobs_2026-09-20.xlsx
@@ -4168,7 +4168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4216,35 +4216,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kiwi</t>
+          <t>Log9 Materials</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.gokiwi.in/careers</t>
+          <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.gokiwi.in/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Log9 Materials</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.log9materials.com/careers</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4253,18 +4233,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4273,6 +4253,26 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vymo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://getvymo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://getvymo.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -4416,15 +4416,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4433,18 +4453,38 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shiprocket</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.shiprocket.in/careers/</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4453,18 +4493,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4473,38 +4513,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>upGrad</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://www.upgrad.com/careers/</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.upgrad.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
